--- a/upload/scm_po_converted.xlsx
+++ b/upload/scm_po_converted.xlsx
@@ -122,7 +122,7 @@
     <t>230769</t>
   </si>
   <si>
-    <t>3887ATE2-S</t>
+    <t>3887ATEV</t>
   </si>
   <si>
     <t>PEN</t>

--- a/upload/scm_po_converted.xlsx
+++ b/upload/scm_po_converted.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="76">
   <si>
     <t>Customer PO No.</t>
   </si>
@@ -119,10 +119,10 @@
     <t>Shipping Method</t>
   </si>
   <si>
-    <t>230769</t>
-  </si>
-  <si>
-    <t>3887ATEV</t>
+    <t>229859</t>
+  </si>
+  <si>
+    <t>3887ATE2-S</t>
   </si>
   <si>
     <t>PEN</t>
@@ -131,100 +131,118 @@
     <t>20240430</t>
   </si>
   <si>
-    <t>55NANO77SRA.AWF</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>2032.67</t>
-  </si>
-  <si>
-    <t>20240418</t>
+    <t>LS66SDP.APZGLPR</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>4971.65</t>
+  </si>
+  <si>
+    <t>20240401</t>
   </si>
   <si>
     <t>ESTILOS S.R.L.</t>
   </si>
   <si>
-    <t>55UR7300PSA.AWFQ</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>1783.66</t>
-  </si>
-  <si>
-    <t>65NANO77SRA.AWF</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>3070.17</t>
-  </si>
-  <si>
-    <t>65UR7300PSA.AWFQ</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>2323.17</t>
-  </si>
-  <si>
-    <t>No SKU: 2306300</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>2377.18</t>
-  </si>
-  <si>
-    <t>No SKU: 2306301</t>
-  </si>
-  <si>
-    <t>1319.12</t>
-  </si>
-  <si>
-    <t>75UR8750PSA.AWF</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>3033.18</t>
-  </si>
-  <si>
-    <t>No SKU: 2306303</t>
-  </si>
-  <si>
-    <t>2869.18</t>
-  </si>
-  <si>
-    <t>86UR8750PSA.AWF</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>6149.18</t>
-  </si>
-  <si>
-    <t>No SKU: 2306306</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3689.18</t>
-  </si>
-  <si>
-    <t>No SKU: 2306308</t>
-  </si>
-  <si>
-    <t>10659.18</t>
+    <t>LS66SXN.APZGLPR</t>
+  </si>
+  <si>
+    <t>6416.65</t>
+  </si>
+  <si>
+    <t>GT37SGP.APZGLPR</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>1954.15</t>
+  </si>
+  <si>
+    <t>GT24BPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>1444.15</t>
+  </si>
+  <si>
+    <t>GT31WPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>1699.15</t>
+  </si>
+  <si>
+    <t>GT31BPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1656.65</t>
+  </si>
+  <si>
+    <t>GT33BPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>1741.64</t>
+  </si>
+  <si>
+    <t>WT16BPB.ABMGLGP</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1529.15</t>
+  </si>
+  <si>
+    <t>WT19DV6.ASFGLGP</t>
+  </si>
+  <si>
+    <t>1784.15</t>
+  </si>
+  <si>
+    <t>WT17BV6.ABMGLGP</t>
+  </si>
+  <si>
+    <t>WT21VV6.ASSGLGP</t>
+  </si>
+  <si>
+    <t>2081.65</t>
+  </si>
+  <si>
+    <t>WT21PBV6.APBGLGP</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>2166.65</t>
+  </si>
+  <si>
+    <t>WT13DPBK.ASFGLGP</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>1231.65</t>
+  </si>
+  <si>
+    <t>MH7032JAS.BBKGLPR</t>
+  </si>
+  <si>
+    <t>415.66</t>
   </si>
 </sst>
 </file>
@@ -564,7 +582,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -742,10 +760,10 @@
         <v>43</v>
       </c>
       <c r="F3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" t="s">
         <v>44</v>
-      </c>
-      <c r="G3" t="s">
-        <v>45</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -793,13 +811,13 @@
         <v>37</v>
       </c>
       <c r="E4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
         <v>46</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>47</v>
-      </c>
-      <c r="G4" t="s">
-        <v>48</v>
       </c>
       <c r="H4"/>
       <c r="I4"/>
@@ -847,13 +865,13 @@
         <v>37</v>
       </c>
       <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
         <v>49</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>50</v>
-      </c>
-      <c r="G5" t="s">
-        <v>51</v>
       </c>
       <c r="H5"/>
       <c r="I5"/>
@@ -901,13 +919,13 @@
         <v>37</v>
       </c>
       <c r="E6" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" t="s">
         <v>52</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>53</v>
-      </c>
-      <c r="G6" t="s">
-        <v>54</v>
       </c>
       <c r="H6"/>
       <c r="I6"/>
@@ -955,10 +973,10 @@
         <v>37</v>
       </c>
       <c r="E7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
         <v>55</v>
-      </c>
-      <c r="F7" t="s">
-        <v>53</v>
       </c>
       <c r="G7" t="s">
         <v>56</v>
@@ -1066,10 +1084,10 @@
         <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H9"/>
       <c r="I9"/>
@@ -1117,10 +1135,10 @@
         <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="G10" t="s">
         <v>64</v>
@@ -1174,10 +1192,10 @@
         <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
@@ -1225,13 +1243,13 @@
         <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H12"/>
       <c r="I12"/>
@@ -1264,6 +1282,168 @@
       <c r="AF12"/>
       <c r="AG12"/>
       <c r="AH12"/>
+    </row>
+    <row r="13" spans="1:34">
+      <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13" t="s">
+        <v>41</v>
+      </c>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="Z13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA13"/>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
+      <c r="AE13"/>
+      <c r="AF13"/>
+      <c r="AG13"/>
+      <c r="AH13"/>
+    </row>
+    <row r="14" spans="1:34">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14" t="s">
+        <v>41</v>
+      </c>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA14"/>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
+      <c r="AE14"/>
+      <c r="AF14"/>
+      <c r="AG14"/>
+      <c r="AH14"/>
+    </row>
+    <row r="15" spans="1:34">
+      <c r="A15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" t="s">
+        <v>75</v>
+      </c>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA15"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15"/>
+      <c r="AF15"/>
+      <c r="AG15"/>
+      <c r="AH15"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>

--- a/upload/scm_po_converted.xlsx
+++ b/upload/scm_po_converted.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="81">
   <si>
     <t>Customer PO No.</t>
   </si>
@@ -119,7 +119,7 @@
     <t>Shipping Method</t>
   </si>
   <si>
-    <t>S.A.</t>
+    <t>4219517</t>
   </si>
   <si>
     <t>6374LURIN2-S</t>
@@ -128,19 +128,136 @@
     <t>PEN</t>
   </si>
   <si>
-    <t>No SKU: 7</t>
+    <t>20240312</t>
+  </si>
+  <si>
+    <t>GT37SGP.APZGLPR</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>1602.64</t>
+  </si>
+  <si>
+    <t>20240304</t>
+  </si>
+  <si>
+    <t>SODIMAC</t>
+  </si>
+  <si>
+    <t>4219518</t>
+  </si>
+  <si>
+    <t>WT13BPBK.ABMGLGP</t>
+  </si>
+  <si>
+    <t>1006.03</t>
+  </si>
+  <si>
+    <t>4219519</t>
+  </si>
+  <si>
+    <t>4219520</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>4219522</t>
+  </si>
+  <si>
+    <t>GB37WGT.AMCGLPR</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>9.</t>
-  </si>
-  <si>
-    <t>LG ELECTRONICS PERU</t>
-  </si>
-  <si>
-    <t>SODIMAC</t>
+    <t>2236.54</t>
+  </si>
+  <si>
+    <t>LS51BPP.AHSGLPR</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1938.24</t>
+  </si>
+  <si>
+    <t>GT31WPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>1416.2</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>4219524</t>
+  </si>
+  <si>
+    <t>GT24BPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>1155.19</t>
+  </si>
+  <si>
+    <t>4219525</t>
+  </si>
+  <si>
+    <t>WT17BV6.ABMGLGP</t>
+  </si>
+  <si>
+    <t>150</t>
+  </si>
+  <si>
+    <t>1453.49</t>
+  </si>
+  <si>
+    <t>4219526</t>
+  </si>
+  <si>
+    <t>141</t>
+  </si>
+  <si>
+    <t>4219528</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>4219529</t>
+  </si>
+  <si>
+    <t>MS2032GAS.BBKGLPR</t>
+  </si>
+  <si>
+    <t>290.8</t>
+  </si>
+  <si>
+    <t>4219530</t>
+  </si>
+  <si>
+    <t>WD9PVC4S6.APTGLGP</t>
+  </si>
+  <si>
+    <t>1565.36</t>
+  </si>
+  <si>
+    <t>GT31BPP.APZGLPR</t>
+  </si>
+  <si>
+    <t>78</t>
+  </si>
+  <si>
+    <t>1341.63</t>
   </si>
 </sst>
 </file>
@@ -480,7 +597,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -597,15 +714,17 @@
       <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="D2"/>
+      <c r="D2" t="s">
+        <v>37</v>
+      </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H2"/>
       <c r="I2"/>
@@ -613,7 +732,7 @@
       <c r="K2"/>
       <c r="L2"/>
       <c r="M2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N2"/>
       <c r="O2"/>
@@ -628,7 +747,7 @@
       <c r="X2"/>
       <c r="Y2"/>
       <c r="Z2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA2"/>
       <c r="AB2"/>
@@ -641,7 +760,7 @@
     </row>
     <row r="3" spans="1:34">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
@@ -649,15 +768,17 @@
       <c r="C3" t="s">
         <v>36</v>
       </c>
-      <c r="D3"/>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H3"/>
       <c r="I3"/>
@@ -665,7 +786,7 @@
       <c r="K3"/>
       <c r="L3"/>
       <c r="M3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N3"/>
       <c r="O3"/>
@@ -680,7 +801,7 @@
       <c r="X3"/>
       <c r="Y3"/>
       <c r="Z3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AA3"/>
       <c r="AB3"/>
@@ -690,6 +811,762 @@
       <c r="AF3"/>
       <c r="AG3"/>
       <c r="AH3"/>
+    </row>
+    <row r="4" spans="1:34">
+      <c r="A4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
+      <c r="R4"/>
+      <c r="S4"/>
+      <c r="T4"/>
+      <c r="U4"/>
+      <c r="V4"/>
+      <c r="W4"/>
+      <c r="X4"/>
+      <c r="Y4"/>
+      <c r="Z4" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA4"/>
+      <c r="AB4"/>
+      <c r="AC4"/>
+      <c r="AD4"/>
+      <c r="AE4"/>
+      <c r="AF4"/>
+      <c r="AG4"/>
+      <c r="AH4"/>
+    </row>
+    <row r="5" spans="1:34">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" t="s">
+        <v>45</v>
+      </c>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+      <c r="S5"/>
+      <c r="T5"/>
+      <c r="U5"/>
+      <c r="V5"/>
+      <c r="W5"/>
+      <c r="X5"/>
+      <c r="Y5"/>
+      <c r="Z5" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA5"/>
+      <c r="AB5"/>
+      <c r="AC5"/>
+      <c r="AD5"/>
+      <c r="AE5"/>
+      <c r="AF5"/>
+      <c r="AG5"/>
+      <c r="AH5"/>
+    </row>
+    <row r="6" spans="1:34">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
+      <c r="R6"/>
+      <c r="S6"/>
+      <c r="T6"/>
+      <c r="U6"/>
+      <c r="V6"/>
+      <c r="W6"/>
+      <c r="X6"/>
+      <c r="Y6"/>
+      <c r="Z6" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA6"/>
+      <c r="AB6"/>
+      <c r="AC6"/>
+      <c r="AD6"/>
+      <c r="AE6"/>
+      <c r="AF6"/>
+      <c r="AG6"/>
+      <c r="AH6"/>
+    </row>
+    <row r="7" spans="1:34">
+      <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
+      <c r="R7"/>
+      <c r="S7"/>
+      <c r="T7"/>
+      <c r="U7"/>
+      <c r="V7"/>
+      <c r="W7"/>
+      <c r="X7"/>
+      <c r="Y7"/>
+      <c r="Z7" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA7"/>
+      <c r="AB7"/>
+      <c r="AC7"/>
+      <c r="AD7"/>
+      <c r="AE7"/>
+      <c r="AF7"/>
+      <c r="AG7"/>
+      <c r="AH7"/>
+    </row>
+    <row r="8" spans="1:34">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+      <c r="S8"/>
+      <c r="T8"/>
+      <c r="U8"/>
+      <c r="V8"/>
+      <c r="W8"/>
+      <c r="X8"/>
+      <c r="Y8"/>
+      <c r="Z8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA8"/>
+      <c r="AB8"/>
+      <c r="AC8"/>
+      <c r="AD8"/>
+      <c r="AE8"/>
+      <c r="AF8"/>
+      <c r="AG8"/>
+      <c r="AH8"/>
+    </row>
+    <row r="9" spans="1:34">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9"/>
+      <c r="L9"/>
+      <c r="M9" t="s">
+        <v>41</v>
+      </c>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
+      <c r="R9"/>
+      <c r="S9"/>
+      <c r="T9"/>
+      <c r="U9"/>
+      <c r="V9"/>
+      <c r="W9"/>
+      <c r="X9"/>
+      <c r="Y9"/>
+      <c r="Z9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA9"/>
+      <c r="AB9"/>
+      <c r="AC9"/>
+      <c r="AD9"/>
+      <c r="AE9"/>
+      <c r="AF9"/>
+      <c r="AG9"/>
+      <c r="AH9"/>
+    </row>
+    <row r="10" spans="1:34">
+      <c r="A10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10"/>
+      <c r="I10"/>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+      <c r="M10" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
+      <c r="R10"/>
+      <c r="S10"/>
+      <c r="T10"/>
+      <c r="U10"/>
+      <c r="V10"/>
+      <c r="W10"/>
+      <c r="X10"/>
+      <c r="Y10"/>
+      <c r="Z10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA10"/>
+      <c r="AB10"/>
+      <c r="AC10"/>
+      <c r="AD10"/>
+      <c r="AE10"/>
+      <c r="AF10"/>
+      <c r="AG10"/>
+      <c r="AH10"/>
+    </row>
+    <row r="11" spans="1:34">
+      <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>63</v>
+      </c>
+      <c r="H11"/>
+      <c r="I11"/>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+      <c r="M11" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
+      <c r="R11"/>
+      <c r="S11"/>
+      <c r="T11"/>
+      <c r="U11"/>
+      <c r="V11"/>
+      <c r="W11"/>
+      <c r="X11"/>
+      <c r="Y11"/>
+      <c r="Z11" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA11"/>
+      <c r="AB11"/>
+      <c r="AC11"/>
+      <c r="AD11"/>
+      <c r="AE11"/>
+      <c r="AF11"/>
+      <c r="AG11"/>
+      <c r="AH11"/>
+    </row>
+    <row r="12" spans="1:34">
+      <c r="A12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" t="s">
+        <v>67</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+      <c r="M12" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+      <c r="S12"/>
+      <c r="T12"/>
+      <c r="U12"/>
+      <c r="V12"/>
+      <c r="W12"/>
+      <c r="X12"/>
+      <c r="Y12"/>
+      <c r="Z12" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA12"/>
+      <c r="AB12"/>
+      <c r="AC12"/>
+      <c r="AD12"/>
+      <c r="AE12"/>
+      <c r="AF12"/>
+      <c r="AG12"/>
+      <c r="AH12"/>
+    </row>
+    <row r="13" spans="1:34">
+      <c r="A13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" t="s">
+        <v>63</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+      <c r="M13" t="s">
+        <v>41</v>
+      </c>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+      <c r="V13"/>
+      <c r="W13"/>
+      <c r="X13"/>
+      <c r="Y13"/>
+      <c r="Z13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA13"/>
+      <c r="AB13"/>
+      <c r="AC13"/>
+      <c r="AD13"/>
+      <c r="AE13"/>
+      <c r="AF13"/>
+      <c r="AG13"/>
+      <c r="AH13"/>
+    </row>
+    <row r="14" spans="1:34">
+      <c r="A14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+      <c r="M14" t="s">
+        <v>41</v>
+      </c>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
+      <c r="R14"/>
+      <c r="S14"/>
+      <c r="T14"/>
+      <c r="U14"/>
+      <c r="V14"/>
+      <c r="W14"/>
+      <c r="X14"/>
+      <c r="Y14"/>
+      <c r="Z14" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA14"/>
+      <c r="AB14"/>
+      <c r="AC14"/>
+      <c r="AD14"/>
+      <c r="AE14"/>
+      <c r="AF14"/>
+      <c r="AG14"/>
+      <c r="AH14"/>
+    </row>
+    <row r="15" spans="1:34">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="G15" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+      <c r="M15" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
+      <c r="R15"/>
+      <c r="S15"/>
+      <c r="T15"/>
+      <c r="U15"/>
+      <c r="V15"/>
+      <c r="W15"/>
+      <c r="X15"/>
+      <c r="Y15"/>
+      <c r="Z15" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA15"/>
+      <c r="AB15"/>
+      <c r="AC15"/>
+      <c r="AD15"/>
+      <c r="AE15"/>
+      <c r="AF15"/>
+      <c r="AG15"/>
+      <c r="AH15"/>
+    </row>
+    <row r="16" spans="1:34">
+      <c r="A16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+      <c r="M16" t="s">
+        <v>41</v>
+      </c>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
+      <c r="R16"/>
+      <c r="S16"/>
+      <c r="T16"/>
+      <c r="U16"/>
+      <c r="V16"/>
+      <c r="W16"/>
+      <c r="X16"/>
+      <c r="Y16"/>
+      <c r="Z16" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA16"/>
+      <c r="AB16"/>
+      <c r="AC16"/>
+      <c r="AD16"/>
+      <c r="AE16"/>
+      <c r="AF16"/>
+      <c r="AG16"/>
+      <c r="AH16"/>
+    </row>
+    <row r="17" spans="1:34">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+      <c r="M17" t="s">
+        <v>41</v>
+      </c>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
+      <c r="R17"/>
+      <c r="S17"/>
+      <c r="T17"/>
+      <c r="U17"/>
+      <c r="V17"/>
+      <c r="W17"/>
+      <c r="X17"/>
+      <c r="Y17"/>
+      <c r="Z17" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA17"/>
+      <c r="AB17"/>
+      <c r="AC17"/>
+      <c r="AD17"/>
+      <c r="AE17"/>
+      <c r="AF17"/>
+      <c r="AG17"/>
+      <c r="AH17"/>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>

--- a/upload/scm_po_converted.xlsx
+++ b/upload/scm_po_converted.xlsx
@@ -131,7 +131,7 @@
     <t>WT13DPBK.ASFGLGP</t>
   </si>
   <si>
-    <t>TIENDAS CHANCAFE S.A.C.</t>
+    <t>CHANCAFE</t>
   </si>
   <si>
     <t>No SKU: WT17BV6T</t>
